--- a/resolveIssues/ig/StructureDefinition-fr-encounter-document.xlsx
+++ b/resolveIssues/ig/StructureDefinition-fr-encounter-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-03T07:56:38+00:00</t>
+    <t>2026-06-04T08:54:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -939,13 +939,13 @@
     <t>Encounter.class</t>
   </si>
   <si>
-    <t>Type de rencontre (JDV_HL7_ActEncounterCode_CISIS ou JDV spécifique au volet)</t>
+    <t>Type de rencontre (codes HL7 ActEncounterCode ou codes spécifiques au volet)</t>
   </si>
   <si>
     <t>Concepts representing classification of patient encounter such as ambulatory (outpatient), inpatient, emergency, home health or others due to local variations.</t>
   </si>
   <si>
-    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-hl7-v3-ActEncounterCode-cisis</t>
+    <t>https://interop.esante.gouv.fr/ig/document/core/ValueSet/fr-vs-encounter-class</t>
   </si>
   <si>
     <t>.inboundRelationship[typeCode=SUBJ].source[classCode=LIST].code</t>

--- a/resolveIssues/ig/StructureDefinition-fr-encounter-document.xlsx
+++ b/resolveIssues/ig/StructureDefinition-fr-encounter-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-04T08:54:45+00:00</t>
+    <t>2026-06-04T14:47:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
